--- a/SSIS-Project/Timesheets/Buhle/Buhle_Mukhuba_March_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Buhle/Buhle_Mukhuba_March_FinalWeek.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://northerndata-my.sharepoint.com/personal/buhle_mukhuba_sambeconsulting_com/Documents/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_TeolanGovender_2026\SSIS-Project\Timesheets\Buhle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{7E45E865-ED97-4E5F-8A35-A2A68DE5DF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B08C5DF0-3CFA-445B-B5E8-7A628D8C814D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E531877-99BB-4008-B1F2-A257D126D609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Mar" sheetId="6" r:id="rId1"/>
     <sheet name="Key" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -634,9 +633,6 @@
     <t>Buhle</t>
   </si>
   <si>
-    <t xml:space="preserve">Attended onboarding meeting and started working on dream board </t>
-  </si>
-  <si>
     <t>Continued working on dream board</t>
   </si>
   <si>
@@ -725,6 +721,9 @@
   </si>
   <si>
     <t>Udemy course - Excel for beginners</t>
+  </si>
+  <si>
+    <t>Attended onboarding meeting and started working on dream board update</t>
   </si>
 </sst>
 </file>
@@ -1764,10 +1763,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H77" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
   <autoFilter ref="H2:H77" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}"/>
@@ -2062,18 +2057,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1366D5-46F5-410C-BC9F-D56DCF566D28}">
   <dimension ref="A5:J187"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="21" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="21" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="21" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="21" customWidth="1"/>
     <col min="4" max="5" width="20" style="21" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="21" customWidth="1"/>
     <col min="7" max="7" width="34" style="21" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="21"/>
+    <col min="8" max="16384" width="8.75" style="21"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A5" s="35" t="s">
         <v>2</v>
       </c>
@@ -2083,7 +2078,7 @@
       <c r="C5" s="35"/>
       <c r="H5" s="38"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A6" s="35" t="s">
         <v>91</v>
       </c>
@@ -2097,10 +2092,10 @@
       <c r="H6" s="38"/>
       <c r="J6" s="39"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="H7" s="38"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A8" s="22" t="s">
         <v>0</v>
       </c>
@@ -2132,7 +2127,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A9" s="29">
         <v>46082</v>
       </c>
@@ -2151,7 +2146,7 @@
       <c r="I9" s="33"/>
       <c r="J9" s="33"/>
     </row>
-    <row r="10" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A10" s="20">
         <v>46083</v>
       </c>
@@ -2169,7 +2164,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="H10" s="27">
         <f>J10-I10</f>
@@ -2200,7 +2195,7 @@
         <v>15</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H11" s="27">
         <f>J11-I11</f>
@@ -2213,7 +2208,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A12" s="20">
         <v>46084</v>
       </c>
@@ -2231,7 +2226,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H12" s="27">
         <f t="shared" ref="H12:H84" si="0">J12-I12</f>
@@ -2244,7 +2239,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A13" s="20">
         <v>46085</v>
       </c>
@@ -2262,7 +2257,7 @@
         <v>15</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H13" s="27">
         <f t="shared" si="0"/>
@@ -2275,7 +2270,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A14" s="20">
         <v>46085</v>
       </c>
@@ -2293,7 +2288,7 @@
         <v>15</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H14" s="27">
         <f t="shared" si="0"/>
@@ -2306,7 +2301,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A15" s="20">
         <v>46085</v>
       </c>
@@ -2324,7 +2319,7 @@
         <v>15</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H15" s="27">
         <f t="shared" si="0"/>
@@ -2337,7 +2332,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A16" s="20">
         <v>46085</v>
       </c>
@@ -2355,7 +2350,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H16" s="27">
         <f t="shared" si="0"/>
@@ -2368,7 +2363,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A17" s="20">
         <v>46086</v>
       </c>
@@ -2386,7 +2381,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H17" s="27">
         <f t="shared" si="0"/>
@@ -2399,7 +2394,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A18" s="20">
         <v>46086</v>
       </c>
@@ -2417,7 +2412,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H18" s="27">
         <f t="shared" si="0"/>
@@ -2430,7 +2425,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A19" s="20">
         <v>46086</v>
       </c>
@@ -2448,7 +2443,7 @@
         <v>15</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H19" s="27">
         <f t="shared" si="0"/>
@@ -2461,7 +2456,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A20" s="20">
         <v>46086</v>
       </c>
@@ -2479,7 +2474,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H20" s="27">
         <f t="shared" si="0"/>
@@ -2492,7 +2487,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A21" s="20">
         <v>46087</v>
       </c>
@@ -2510,7 +2505,7 @@
         <v>15</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H21" s="27">
         <f t="shared" si="0"/>
@@ -2523,7 +2518,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A22" s="20">
         <v>46087</v>
       </c>
@@ -2541,7 +2536,7 @@
         <v>15</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H22" s="27">
         <f t="shared" si="0"/>
@@ -2554,7 +2549,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A23" s="20">
         <v>46087</v>
       </c>
@@ -2572,7 +2567,7 @@
         <v>15</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H23" s="27">
         <f t="shared" si="0"/>
@@ -2585,7 +2580,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A24" s="20">
         <v>46087</v>
       </c>
@@ -2603,7 +2598,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H24" s="27">
         <f t="shared" si="0"/>
@@ -2616,7 +2611,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A25" s="20">
         <v>46087</v>
       </c>
@@ -2634,7 +2629,7 @@
         <v>15</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H25" s="27">
         <f t="shared" si="0"/>
@@ -2647,7 +2642,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A26" s="20">
         <v>46087</v>
       </c>
@@ -2665,7 +2660,7 @@
         <v>15</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H26" s="27">
         <f>J26-I26</f>
@@ -2678,7 +2673,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A27" s="29">
         <v>46088</v>
       </c>
@@ -2697,7 +2692,7 @@
       <c r="I27" s="33"/>
       <c r="J27" s="33"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A28" s="29">
         <v>46089</v>
       </c>
@@ -2716,7 +2711,7 @@
       <c r="I28" s="33"/>
       <c r="J28" s="33"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A29" s="20">
         <v>46090</v>
       </c>
@@ -2734,7 +2729,7 @@
         <v>15</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H29" s="27">
         <f t="shared" si="0"/>
@@ -2747,7 +2742,7 @@
         <v>0.35416666666666669</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A30" s="20">
         <v>46090</v>
       </c>
@@ -2765,7 +2760,7 @@
         <v>15</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H30" s="27">
         <f t="shared" si="0"/>
@@ -2778,7 +2773,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A31" s="20">
         <v>46090</v>
       </c>
@@ -2796,7 +2791,7 @@
         <v>15</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H31" s="27">
         <f t="shared" si="0"/>
@@ -2809,7 +2804,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A32" s="20">
         <v>46090</v>
       </c>
@@ -2827,7 +2822,7 @@
         <v>15</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H32" s="27">
         <f t="shared" si="0"/>
@@ -2840,7 +2835,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A33" s="20">
         <v>46090</v>
       </c>
@@ -2858,7 +2853,7 @@
         <v>15</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H33" s="27">
         <f t="shared" si="0"/>
@@ -2871,7 +2866,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A34" s="20">
         <v>46090</v>
       </c>
@@ -2889,7 +2884,7 @@
         <v>15</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H34" s="27">
         <f t="shared" si="0"/>
@@ -2902,7 +2897,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A35" s="20">
         <v>46090</v>
       </c>
@@ -2920,7 +2915,7 @@
         <v>15</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H35" s="27">
         <f t="shared" si="0"/>
@@ -2933,7 +2928,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A36" s="20">
         <v>46091</v>
       </c>
@@ -2951,7 +2946,7 @@
         <v>15</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H36" s="27">
         <f t="shared" si="0"/>
@@ -2964,7 +2959,7 @@
         <v>0.35416666666666669</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A37" s="20">
         <v>46091</v>
       </c>
@@ -2982,7 +2977,7 @@
         <v>15</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H37" s="27">
         <f t="shared" si="0"/>
@@ -2995,7 +2990,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A38" s="20">
         <v>46091</v>
       </c>
@@ -3013,7 +3008,7 @@
         <v>15</v>
       </c>
       <c r="G38" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H38" s="27">
         <f t="shared" si="0"/>
@@ -3026,7 +3021,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A39" s="20">
         <v>46091</v>
       </c>
@@ -3044,7 +3039,7 @@
         <v>15</v>
       </c>
       <c r="G39" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H39" s="27">
         <f t="shared" si="0"/>
@@ -3057,7 +3052,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
       <c r="A40" s="20">
         <v>46091</v>
       </c>
@@ -3075,7 +3070,7 @@
         <v>15</v>
       </c>
       <c r="G40" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H40" s="27">
         <f t="shared" si="0"/>
@@ -3088,7 +3083,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A41" s="20">
         <v>46091</v>
       </c>
@@ -3106,7 +3101,7 @@
         <v>15</v>
       </c>
       <c r="G41" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H41" s="27">
         <f t="shared" si="0"/>
@@ -3119,7 +3114,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A42" s="20">
         <v>46092</v>
       </c>
@@ -3137,7 +3132,7 @@
         <v>15</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H42" s="27">
         <f t="shared" si="0"/>
@@ -3150,7 +3145,7 @@
         <v>0.33680555555555558</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A43" s="20">
         <v>46092</v>
       </c>
@@ -3168,7 +3163,7 @@
         <v>15</v>
       </c>
       <c r="G43" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H43" s="27">
         <f t="shared" si="0"/>
@@ -3181,7 +3176,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A44" s="20">
         <v>46092</v>
       </c>
@@ -3199,7 +3194,7 @@
         <v>15</v>
       </c>
       <c r="G44" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H44" s="27">
         <f t="shared" si="0"/>
@@ -3212,7 +3207,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A45" s="20">
         <v>46092</v>
       </c>
@@ -3230,7 +3225,7 @@
         <v>15</v>
       </c>
       <c r="G45" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="0"/>
@@ -3261,7 +3256,7 @@
         <v>15</v>
       </c>
       <c r="G46" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H46" s="27">
         <f t="shared" si="0"/>
@@ -3274,7 +3269,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A47" s="20">
         <v>46092</v>
       </c>
@@ -3291,7 +3286,7 @@
         <v>15</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H47" s="27">
         <f t="shared" si="0"/>
@@ -3322,7 +3317,7 @@
         <v>15</v>
       </c>
       <c r="G48" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H48" s="27">
         <f t="shared" si="0"/>
@@ -3353,7 +3348,7 @@
         <v>15</v>
       </c>
       <c r="G49" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H49" s="27">
         <f t="shared" si="0"/>
@@ -3384,7 +3379,7 @@
         <v>15</v>
       </c>
       <c r="G50" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H50" s="27">
         <f t="shared" si="0"/>
@@ -3415,7 +3410,7 @@
         <v>15</v>
       </c>
       <c r="G51" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H51" s="27">
         <f t="shared" si="0"/>
@@ -3428,7 +3423,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A52" s="20">
         <v>46093</v>
       </c>
@@ -3446,7 +3441,7 @@
         <v>15</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H52" s="27">
         <f t="shared" si="0"/>
@@ -3459,7 +3454,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A53" s="20">
         <v>46093</v>
       </c>
@@ -3477,7 +3472,7 @@
         <v>15</v>
       </c>
       <c r="G53" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H53" s="27">
         <f t="shared" si="0"/>
@@ -3490,7 +3485,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A54" s="20">
         <v>46093</v>
       </c>
@@ -3508,7 +3503,7 @@
         <v>15</v>
       </c>
       <c r="G54" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H54" s="27">
         <f t="shared" si="0"/>
@@ -3539,7 +3534,7 @@
         <v>15</v>
       </c>
       <c r="G55" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="0"/>
@@ -3570,7 +3565,7 @@
         <v>15</v>
       </c>
       <c r="G56" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H56" s="27">
         <f t="shared" si="0"/>
@@ -3601,7 +3596,7 @@
         <v>15</v>
       </c>
       <c r="G57" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H57" s="27">
         <f t="shared" si="0"/>
@@ -3614,7 +3609,7 @@
         <v>0.43055555555555558</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A58" s="20">
         <v>46094</v>
       </c>
@@ -3632,7 +3627,7 @@
         <v>15</v>
       </c>
       <c r="G58" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H58" s="27">
         <f t="shared" si="0"/>
@@ -3645,7 +3640,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A59" s="20">
         <v>46094</v>
       </c>
@@ -3663,7 +3658,7 @@
         <v>15</v>
       </c>
       <c r="G59" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H59" s="27">
         <f t="shared" si="0"/>
@@ -3694,7 +3689,7 @@
         <v>15</v>
       </c>
       <c r="G60" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H60" s="27">
         <f t="shared" si="0"/>
@@ -3707,7 +3702,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A61" s="20">
         <v>46094</v>
       </c>
@@ -3725,7 +3720,7 @@
         <v>15</v>
       </c>
       <c r="G61" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H61" s="27">
         <f t="shared" si="0"/>
@@ -3738,7 +3733,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A62" s="20">
         <v>46094</v>
       </c>
@@ -3756,7 +3751,7 @@
         <v>15</v>
       </c>
       <c r="G62" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H62" s="27">
         <f t="shared" si="0"/>
@@ -3787,7 +3782,7 @@
         <v>15</v>
       </c>
       <c r="G63" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H63" s="27">
         <f t="shared" si="0"/>
@@ -3856,7 +3851,7 @@
         <v>15</v>
       </c>
       <c r="G66" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H66" s="27">
         <f t="shared" si="0"/>
@@ -3869,7 +3864,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A67" s="20">
         <v>46097</v>
       </c>
@@ -3887,7 +3882,7 @@
         <v>15</v>
       </c>
       <c r="G67" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H67" s="27">
         <f t="shared" si="0"/>
@@ -3918,7 +3913,7 @@
         <v>15</v>
       </c>
       <c r="G68" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H68" s="27">
         <f t="shared" si="0"/>
@@ -3931,7 +3926,7 @@
         <v>0.42708333333333331</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A69" s="20">
         <v>46097</v>
       </c>
@@ -3949,7 +3944,7 @@
         <v>15</v>
       </c>
       <c r="G69" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H69" s="27">
         <f t="shared" si="0"/>
@@ -3980,7 +3975,7 @@
         <v>15</v>
       </c>
       <c r="G70" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H70" s="27">
         <f t="shared" si="0"/>
@@ -4011,7 +4006,7 @@
         <v>15</v>
       </c>
       <c r="G71" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H71" s="27">
         <f t="shared" si="0"/>
@@ -4042,7 +4037,7 @@
         <v>15</v>
       </c>
       <c r="G72" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H72" s="27">
         <f t="shared" si="0"/>
@@ -4055,7 +4050,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A73" s="20">
         <v>46097</v>
       </c>
@@ -4073,7 +4068,7 @@
         <v>15</v>
       </c>
       <c r="G73" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H73" s="27">
         <f t="shared" si="0"/>
@@ -4104,7 +4099,7 @@
         <v>15</v>
       </c>
       <c r="G74" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H74" s="27">
         <f t="shared" si="0"/>
@@ -4117,7 +4112,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A75" s="20">
         <v>46097</v>
       </c>
@@ -4135,7 +4130,7 @@
         <v>15</v>
       </c>
       <c r="G75" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H75" s="27">
         <f t="shared" si="0"/>
@@ -4166,7 +4161,7 @@
         <v>15</v>
       </c>
       <c r="G76" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H76" s="27">
         <f t="shared" si="0"/>
@@ -4197,7 +4192,7 @@
         <v>15</v>
       </c>
       <c r="G77" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H77" s="27">
         <f t="shared" si="0"/>
@@ -4228,7 +4223,7 @@
         <v>15</v>
       </c>
       <c r="G78" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H78" s="27">
         <f t="shared" si="0"/>
@@ -4241,7 +4236,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A79" s="20">
         <v>46098</v>
       </c>
@@ -4259,7 +4254,7 @@
         <v>15</v>
       </c>
       <c r="G79" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H79" s="27">
         <f t="shared" si="0"/>
@@ -4290,7 +4285,7 @@
         <v>15</v>
       </c>
       <c r="G80" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H80" s="27">
         <f t="shared" si="0"/>
@@ -4321,7 +4316,7 @@
         <v>15</v>
       </c>
       <c r="G81" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H81" s="27">
         <f t="shared" si="0"/>
@@ -4352,7 +4347,7 @@
         <v>15</v>
       </c>
       <c r="G82" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H82" s="27">
         <f t="shared" si="0"/>
@@ -4365,7 +4360,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A83" s="20">
         <v>46098</v>
       </c>
@@ -4383,7 +4378,7 @@
         <v>15</v>
       </c>
       <c r="G83" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H83" s="27">
         <f t="shared" si="0"/>
@@ -4414,7 +4409,7 @@
         <v>15</v>
       </c>
       <c r="G84" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H84" s="27">
         <f t="shared" si="0"/>
@@ -4445,7 +4440,7 @@
         <v>15</v>
       </c>
       <c r="G85" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H85" s="27">
         <f t="shared" ref="H85:H93" si="1">J85-I85</f>
@@ -4476,7 +4471,7 @@
         <v>15</v>
       </c>
       <c r="G86" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H86" s="27">
         <f t="shared" si="1"/>
@@ -4489,7 +4484,7 @@
         <v>0.49722222222222223</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A87" s="20">
         <v>46099</v>
       </c>
@@ -4507,7 +4502,7 @@
         <v>15</v>
       </c>
       <c r="G87" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H87" s="27">
         <f t="shared" si="1"/>
@@ -4528,7 +4523,7 @@
       <c r="E88" s="25"/>
       <c r="F88" s="25"/>
       <c r="G88" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H88" s="27">
         <f t="shared" si="1"/>
@@ -4559,7 +4554,7 @@
         <v>15</v>
       </c>
       <c r="G89" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H89" s="27">
         <f t="shared" si="1"/>
@@ -4572,7 +4567,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A90" s="20">
         <v>46099</v>
       </c>
@@ -4590,7 +4585,7 @@
         <v>15</v>
       </c>
       <c r="G90" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H90" s="27">
         <f t="shared" si="1"/>
@@ -4621,7 +4616,7 @@
         <v>15</v>
       </c>
       <c r="G91" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H91" s="27">
         <f t="shared" si="1"/>
@@ -4634,7 +4629,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A92" s="20">
         <v>46099</v>
       </c>
@@ -4652,7 +4647,7 @@
         <v>15</v>
       </c>
       <c r="G92" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H92" s="27">
         <f t="shared" si="1"/>
@@ -4683,7 +4678,7 @@
         <v>15</v>
       </c>
       <c r="G93" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H93" s="27">
         <f t="shared" si="1"/>
@@ -4714,7 +4709,7 @@
         <v>15</v>
       </c>
       <c r="G94" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H94" s="27">
         <f t="shared" ref="H94:H102" si="2">J94-I94</f>
@@ -4745,7 +4740,7 @@
         <v>15</v>
       </c>
       <c r="G95" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H95" s="27">
         <f t="shared" si="2"/>
@@ -4776,7 +4771,7 @@
         <v>15</v>
       </c>
       <c r="G96" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H96" s="27">
         <f t="shared" si="2"/>
@@ -4807,7 +4802,7 @@
         <v>15</v>
       </c>
       <c r="G97" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H97" s="27">
         <f t="shared" si="2"/>
@@ -4838,7 +4833,7 @@
         <v>15</v>
       </c>
       <c r="G98" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H98" s="27">
         <f t="shared" si="2"/>
@@ -4851,7 +4846,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A99" s="20">
         <v>46100</v>
       </c>
@@ -4869,7 +4864,7 @@
         <v>15</v>
       </c>
       <c r="G99" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H99" s="27">
         <f t="shared" si="2"/>
@@ -4900,7 +4895,7 @@
         <v>15</v>
       </c>
       <c r="G100" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H100" s="27">
         <f t="shared" si="2"/>
@@ -4931,7 +4926,7 @@
         <v>15</v>
       </c>
       <c r="G101" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H101" s="27">
         <f t="shared" si="2"/>
@@ -4944,7 +4939,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A102" s="20">
         <v>46100</v>
       </c>
@@ -4962,7 +4957,7 @@
         <v>15</v>
       </c>
       <c r="G102" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H102" s="27">
         <f t="shared" si="2"/>
@@ -4993,7 +4988,7 @@
         <v>15</v>
       </c>
       <c r="G103" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H103" s="27">
         <f>J103-I103</f>
@@ -5024,7 +5019,7 @@
         <v>15</v>
       </c>
       <c r="G104" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H104" s="27">
         <f t="shared" ref="H104:H112" si="3">J104-I104</f>
@@ -5055,7 +5050,7 @@
         <v>15</v>
       </c>
       <c r="G105" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H105" s="27">
         <f t="shared" si="3"/>
@@ -5086,7 +5081,7 @@
         <v>15</v>
       </c>
       <c r="G106" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H106" s="27">
         <f t="shared" si="3"/>
@@ -5117,7 +5112,7 @@
         <v>15</v>
       </c>
       <c r="G107" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H107" s="27">
         <f t="shared" si="3"/>
@@ -5148,7 +5143,7 @@
         <v>15</v>
       </c>
       <c r="G108" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H108" s="27">
         <f t="shared" si="3"/>
@@ -5161,7 +5156,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A109" s="20">
         <v>46101</v>
       </c>
@@ -5179,7 +5174,7 @@
         <v>15</v>
       </c>
       <c r="G109" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H109" s="27">
         <f t="shared" si="3"/>
@@ -5210,7 +5205,7 @@
         <v>15</v>
       </c>
       <c r="G110" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H110" s="27">
         <f t="shared" si="3"/>
@@ -5223,7 +5218,7 @@
         <v>0.62013888888888891</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A111" s="20">
         <v>46101</v>
       </c>
@@ -5241,7 +5236,7 @@
         <v>15</v>
       </c>
       <c r="G111" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H111" s="27">
         <f t="shared" si="3"/>
@@ -5254,7 +5249,7 @@
         <v>0.62152777777777779</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A112" s="20">
         <v>46101</v>
       </c>
@@ -5272,7 +5267,7 @@
         <v>15</v>
       </c>
       <c r="G112" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H112" s="27">
         <f t="shared" si="3"/>
@@ -5285,7 +5280,7 @@
         <v>0.65972222222222221</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A113" s="20">
         <v>46101</v>
       </c>
@@ -5303,7 +5298,7 @@
         <v>15</v>
       </c>
       <c r="G113" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H113" s="27">
         <f t="shared" ref="H113:H176" si="4">J113-I113</f>
@@ -5384,7 +5379,7 @@
         <v>15</v>
       </c>
       <c r="G116" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H116" s="27">
         <f t="shared" si="4"/>
@@ -5415,7 +5410,7 @@
         <v>15</v>
       </c>
       <c r="G117" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H117" s="27">
         <f t="shared" si="4"/>
@@ -5446,7 +5441,7 @@
         <v>15</v>
       </c>
       <c r="G118" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H118" s="27">
         <f t="shared" si="4"/>
@@ -5477,7 +5472,7 @@
         <v>15</v>
       </c>
       <c r="G119" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H119" s="27">
         <f t="shared" si="4"/>
@@ -5508,7 +5503,7 @@
         <v>15</v>
       </c>
       <c r="G120" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H120" s="27">
         <f t="shared" si="4"/>
@@ -5521,7 +5516,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A121" s="20">
         <v>46104</v>
       </c>
@@ -5539,7 +5534,7 @@
         <v>15</v>
       </c>
       <c r="G121" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H121" s="27">
         <f t="shared" si="4"/>
@@ -5570,7 +5565,7 @@
         <v>15</v>
       </c>
       <c r="G122" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H122" s="27">
         <f t="shared" si="4"/>
@@ -5601,7 +5596,7 @@
         <v>15</v>
       </c>
       <c r="G123" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H123" s="27">
         <f t="shared" si="4"/>
@@ -5614,7 +5609,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A124" s="20">
         <v>46104</v>
       </c>
@@ -5632,7 +5627,7 @@
         <v>15</v>
       </c>
       <c r="G124" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H124" s="27">
         <f t="shared" si="4"/>
@@ -5663,7 +5658,7 @@
         <v>15</v>
       </c>
       <c r="G125" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H125" s="27">
         <f t="shared" si="4"/>
@@ -5694,7 +5689,7 @@
         <v>15</v>
       </c>
       <c r="G126" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H126" s="27">
         <f t="shared" si="4"/>
@@ -5725,7 +5720,7 @@
         <v>15</v>
       </c>
       <c r="G127" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H127" s="27">
         <f t="shared" si="4"/>
@@ -5756,7 +5751,7 @@
         <v>15</v>
       </c>
       <c r="G128" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H128" s="27">
         <f t="shared" si="4"/>
@@ -5787,7 +5782,7 @@
         <v>15</v>
       </c>
       <c r="G129" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H129" s="27">
         <f t="shared" si="4"/>
@@ -5818,7 +5813,7 @@
         <v>15</v>
       </c>
       <c r="G130" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H130" s="27">
         <f t="shared" si="4"/>
@@ -5831,7 +5826,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A131" s="20">
         <v>46105</v>
       </c>
@@ -5849,7 +5844,7 @@
         <v>15</v>
       </c>
       <c r="G131" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H131" s="27">
         <f t="shared" si="4"/>
@@ -5880,7 +5875,7 @@
         <v>15</v>
       </c>
       <c r="G132" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H132" s="27">
         <f t="shared" si="4"/>
@@ -5893,7 +5888,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A133" s="20">
         <v>46105</v>
       </c>
@@ -5911,7 +5906,7 @@
         <v>15</v>
       </c>
       <c r="G133" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H133" s="27">
         <f t="shared" si="4"/>
@@ -5942,7 +5937,7 @@
         <v>15</v>
       </c>
       <c r="G134" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H134" s="27">
         <f t="shared" si="4"/>
@@ -5973,7 +5968,7 @@
         <v>15</v>
       </c>
       <c r="G135" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H135" s="27">
         <f>J135-I135</f>
@@ -6004,7 +5999,7 @@
         <v>15</v>
       </c>
       <c r="G136" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H136" s="27">
         <f t="shared" ref="H136:H144" si="5">J136-I136</f>
@@ -6035,7 +6030,7 @@
         <v>15</v>
       </c>
       <c r="G137" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H137" s="27">
         <f t="shared" si="5"/>
@@ -6066,7 +6061,7 @@
         <v>15</v>
       </c>
       <c r="G138" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H138" s="27">
         <f t="shared" si="5"/>
@@ -6097,7 +6092,7 @@
         <v>15</v>
       </c>
       <c r="G139" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H139" s="27">
         <f t="shared" si="5"/>
@@ -6110,7 +6105,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A140" s="20">
         <v>46106</v>
       </c>
@@ -6128,7 +6123,7 @@
         <v>15</v>
       </c>
       <c r="G140" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H140" s="27">
         <f t="shared" si="5"/>
@@ -6159,7 +6154,7 @@
         <v>15</v>
       </c>
       <c r="G141" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H141" s="27">
         <f t="shared" si="5"/>
@@ -6190,7 +6185,7 @@
         <v>15</v>
       </c>
       <c r="G142" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H142" s="27">
         <f t="shared" si="5"/>
@@ -6203,7 +6198,7 @@
         <v>0.69791666666666663</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A143" s="20">
         <v>46106</v>
       </c>
@@ -6221,7 +6216,7 @@
         <v>15</v>
       </c>
       <c r="G143" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H143" s="27">
         <f t="shared" si="5"/>
@@ -6252,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="G144" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H144" s="27">
         <f t="shared" si="5"/>
@@ -6283,7 +6278,7 @@
         <v>15</v>
       </c>
       <c r="G145" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H145" s="27">
         <f t="shared" si="4"/>
@@ -6314,7 +6309,7 @@
         <v>15</v>
       </c>
       <c r="G146" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H146" s="27">
         <f t="shared" si="4"/>
@@ -6345,7 +6340,7 @@
         <v>15</v>
       </c>
       <c r="G147" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H147" s="27">
         <f t="shared" si="4"/>
@@ -6376,7 +6371,7 @@
         <v>15</v>
       </c>
       <c r="G148" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H148" s="27">
         <f t="shared" si="4"/>
@@ -6407,7 +6402,7 @@
         <v>15</v>
       </c>
       <c r="G149" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H149" s="27">
         <f t="shared" si="4"/>
@@ -6438,7 +6433,7 @@
         <v>15</v>
       </c>
       <c r="G150" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H150" s="27">
         <f t="shared" si="4"/>
@@ -6451,7 +6446,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A151" s="20">
         <v>46107</v>
       </c>
@@ -6469,7 +6464,7 @@
         <v>15</v>
       </c>
       <c r="G151" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H151" s="27">
         <f t="shared" si="4"/>
@@ -6500,7 +6495,7 @@
         <v>15</v>
       </c>
       <c r="G152" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H152" s="27">
         <f t="shared" si="4"/>
@@ -6513,7 +6508,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A153" s="20">
         <v>46107</v>
       </c>
@@ -6531,7 +6526,7 @@
         <v>15</v>
       </c>
       <c r="G153" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H153" s="27">
         <f t="shared" si="4"/>
@@ -6562,7 +6557,7 @@
         <v>15</v>
       </c>
       <c r="G154" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H154" s="27">
         <f t="shared" si="4"/>
@@ -6593,7 +6588,7 @@
         <v>15</v>
       </c>
       <c r="G155" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H155" s="27">
         <f t="shared" si="4"/>
@@ -6606,7 +6601,7 @@
         <v>0.36458333333333331</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A156" s="20">
         <v>46108</v>
       </c>
@@ -6624,7 +6619,7 @@
         <v>15</v>
       </c>
       <c r="G156" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H156" s="27">
         <f t="shared" si="4"/>
@@ -6637,7 +6632,7 @@
         <v>0.40625</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A157" s="20">
         <v>46108</v>
       </c>
@@ -6655,7 +6650,7 @@
         <v>15</v>
       </c>
       <c r="G157" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H157" s="27">
         <f t="shared" si="4"/>
@@ -6686,7 +6681,7 @@
         <v>15</v>
       </c>
       <c r="G158" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H158" s="27">
         <f t="shared" si="4"/>
@@ -6717,7 +6712,7 @@
         <v>15</v>
       </c>
       <c r="G159" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H159" s="27">
         <f t="shared" si="4"/>
@@ -6748,7 +6743,7 @@
         <v>15</v>
       </c>
       <c r="G160" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H160" s="27">
         <f t="shared" si="4"/>
@@ -6779,7 +6774,7 @@
         <v>15</v>
       </c>
       <c r="G161" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H161" s="27">
         <f t="shared" si="4"/>
@@ -6792,7 +6787,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A162" s="20">
         <v>46108</v>
       </c>
@@ -6810,7 +6805,7 @@
         <v>15</v>
       </c>
       <c r="G162" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H162" s="27">
         <f t="shared" si="4"/>
@@ -6879,7 +6874,7 @@
         <v>15</v>
       </c>
       <c r="G165" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H165" s="27">
         <f t="shared" si="4"/>
@@ -6910,7 +6905,7 @@
         <v>15</v>
       </c>
       <c r="G166" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H166" s="27">
         <f t="shared" si="4"/>
@@ -6941,7 +6936,7 @@
         <v>15</v>
       </c>
       <c r="G167" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H167" s="27">
         <f t="shared" si="4"/>
@@ -6972,7 +6967,7 @@
         <v>15</v>
       </c>
       <c r="G168" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H168" s="27">
         <f t="shared" si="4"/>
@@ -7003,7 +6998,7 @@
         <v>15</v>
       </c>
       <c r="G169" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H169" s="27">
         <f t="shared" si="4"/>
@@ -7016,7 +7011,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A170" s="20">
         <v>46111</v>
       </c>
@@ -7034,7 +7029,7 @@
         <v>15</v>
       </c>
       <c r="G170" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H170" s="27">
         <f t="shared" si="4"/>
@@ -7065,7 +7060,7 @@
         <v>15</v>
       </c>
       <c r="G171" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H171" s="27">
         <f t="shared" si="4"/>
@@ -7096,7 +7091,7 @@
         <v>15</v>
       </c>
       <c r="G172" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H172" s="27">
         <f t="shared" si="4"/>
@@ -7127,7 +7122,7 @@
         <v>15</v>
       </c>
       <c r="G173" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H173" s="27">
         <f t="shared" si="4"/>
@@ -7158,7 +7153,7 @@
         <v>15</v>
       </c>
       <c r="G174" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H174" s="27">
         <f t="shared" si="4"/>
@@ -7189,7 +7184,7 @@
         <v>15</v>
       </c>
       <c r="G175" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H175" s="27">
         <f t="shared" si="4"/>
@@ -7220,7 +7215,7 @@
         <v>15</v>
       </c>
       <c r="G176" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H176" s="27">
         <f t="shared" si="4"/>
@@ -7233,7 +7228,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="20">
         <v>46112</v>
       </c>
@@ -7251,7 +7246,7 @@
         <v>15</v>
       </c>
       <c r="G177" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H177" s="27">
         <f t="shared" ref="H177" si="6">J177-I177</f>
@@ -7264,7 +7259,7 @@
         <v>0.71111111111111114</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A178" s="44"/>
       <c r="B178" s="44"/>
       <c r="C178" s="43"/>
@@ -7275,7 +7270,7 @@
       <c r="H178" s="34"/>
       <c r="I178" s="35"/>
     </row>
-    <row r="179" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="3"/>
@@ -7289,7 +7284,7 @@
       </c>
       <c r="H179" s="38"/>
     </row>
-    <row r="180" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="7"/>
@@ -7302,7 +7297,7 @@
       </c>
       <c r="H180" s="38"/>
     </row>
-    <row r="181" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A181" s="87" t="s">
         <v>23</v>
       </c>
@@ -7313,7 +7308,7 @@
       <c r="F181" s="1"/>
       <c r="H181" s="38"/>
     </row>
-    <row r="182" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A182" s="11"/>
       <c r="B182" s="11"/>
       <c r="C182" s="4"/>
@@ -7327,7 +7322,7 @@
       </c>
       <c r="H182" s="36"/>
     </row>
-    <row r="183" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A183" s="88" t="s">
         <v>25</v>
       </c>
@@ -7343,7 +7338,7 @@
       </c>
       <c r="H183" s="38"/>
     </row>
-    <row r="184" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -7357,7 +7352,7 @@
       </c>
       <c r="H184" s="38"/>
     </row>
-    <row r="185" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -7366,7 +7361,7 @@
       <c r="F185" s="1"/>
       <c r="H185" s="38"/>
     </row>
-    <row r="186" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -7377,7 +7372,7 @@
       <c r="F186" s="19"/>
       <c r="H186" s="38"/>
     </row>
-    <row r="187" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E187" s="37"/>
       <c r="H187" s="38"/>
     </row>
@@ -7500,18 +7495,18 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="B2:J77"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69921875" style="49"/>
+    <col min="1" max="1" width="8.75" style="49"/>
     <col min="2" max="2" width="25.5" style="49" customWidth="1"/>
-    <col min="3" max="3" width="8.69921875" style="49"/>
-    <col min="4" max="4" width="19.296875" style="49" customWidth="1"/>
-    <col min="5" max="5" width="8.69921875" style="49"/>
-    <col min="6" max="6" width="21.796875" style="49" customWidth="1"/>
-    <col min="7" max="16384" width="8.69921875" style="49"/>
+    <col min="3" max="3" width="8.75" style="49"/>
+    <col min="4" max="4" width="19.25" style="49" customWidth="1"/>
+    <col min="5" max="5" width="8.75" style="49"/>
+    <col min="6" max="6" width="21.75" style="49" customWidth="1"/>
+    <col min="7" max="16384" width="8.75" style="49"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="61" t="s">
         <v>114</v>
       </c>
@@ -7528,7 +7523,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="61" t="s">
         <v>102</v>
       </c>
@@ -7545,7 +7540,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="61" t="s">
         <v>115</v>
       </c>
@@ -7562,7 +7557,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="61" t="s">
         <v>116</v>
       </c>
@@ -7576,7 +7571,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="61" t="s">
         <v>117</v>
       </c>
@@ -7590,7 +7585,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="61" t="s">
         <v>103</v>
       </c>
@@ -7604,7 +7599,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="61" t="s">
         <v>118</v>
       </c>
@@ -7621,7 +7616,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="61" t="s">
         <v>119</v>
       </c>
@@ -7638,7 +7633,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="61" t="s">
         <v>121</v>
       </c>
@@ -7652,7 +7647,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="61" t="s">
         <v>123</v>
       </c>
@@ -7669,7 +7664,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="61" t="s">
         <v>124</v>
       </c>
@@ -7683,7 +7678,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="61" t="s">
         <v>126</v>
       </c>
@@ -7694,7 +7689,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="61" t="s">
         <v>128</v>
       </c>
@@ -7706,7 +7701,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="61" t="s">
         <v>104</v>
       </c>
@@ -7718,7 +7713,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="61" t="s">
         <v>57</v>
       </c>
@@ -7730,7 +7725,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B17" s="61" t="s">
         <v>131</v>
       </c>
@@ -7742,7 +7737,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="61" t="s">
         <v>133</v>
       </c>
@@ -7754,7 +7749,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="61" t="s">
         <v>135</v>
       </c>
@@ -7766,7 +7761,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="61" t="s">
         <v>136</v>
       </c>
@@ -7778,7 +7773,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="61" t="s">
         <v>105</v>
       </c>
@@ -7790,7 +7785,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="61" t="s">
         <v>137</v>
       </c>
@@ -7802,7 +7797,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="61" t="s">
         <v>138</v>
       </c>
@@ -7814,7 +7809,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="61" t="s">
         <v>139</v>
       </c>
@@ -7826,7 +7821,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="61" t="s">
         <v>140</v>
       </c>
@@ -7838,7 +7833,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="61" t="s">
         <v>142</v>
       </c>
@@ -7849,7 +7844,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="61" t="s">
         <v>191</v>
       </c>
@@ -7861,7 +7856,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="61" t="s">
         <v>143</v>
       </c>
@@ -7873,7 +7868,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="61" t="s">
         <v>144</v>
       </c>
@@ -7884,7 +7879,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="61" t="s">
         <v>77</v>
       </c>
@@ -7895,7 +7890,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="61" t="s">
         <v>146</v>
       </c>
@@ -7906,7 +7901,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="61" t="s">
         <v>82</v>
       </c>
@@ -7917,7 +7912,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="61" t="s">
         <v>147</v>
       </c>
@@ -7928,7 +7923,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="61" t="s">
         <v>149</v>
       </c>
@@ -7939,7 +7934,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="61" t="s">
         <v>150</v>
       </c>
@@ -7950,7 +7945,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="61" t="s">
         <v>152</v>
       </c>
@@ -7961,7 +7956,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="61" t="s">
         <v>153</v>
       </c>
@@ -7972,7 +7967,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="61" t="s">
         <v>89</v>
       </c>
@@ -7983,7 +7978,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="49" t="s">
         <v>192</v>
       </c>
@@ -7994,7 +7989,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="61" t="s">
         <v>97</v>
       </c>
@@ -8005,7 +8000,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="61" t="s">
         <v>155</v>
       </c>
@@ -8014,7 +8009,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="61" t="s">
         <v>156</v>
       </c>
@@ -8022,7 +8017,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="49" t="s">
         <v>196</v>
       </c>
@@ -8030,174 +8025,174 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B44" s="59"/>
       <c r="H44" s="79" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H45" s="64" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H46" s="83" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B47" s="59"/>
       <c r="H47" s="82" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H48" s="84" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="49" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H49" s="70" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H50" s="77" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H51" s="81" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="52" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H52" s="65" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="53" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H53" s="65" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="54" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H54" s="82" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="55" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H55" s="65" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="56" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H56" s="82" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H57" s="65" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H58" s="82" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="59" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H59" s="64" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H60" s="82" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="61" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H61" s="64" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H62" s="81" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="63" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H63" s="79" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="64" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H64" s="65" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H65" s="82" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H66" s="81" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H67" s="79" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H68" s="65" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H69" s="65" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H70" s="82" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H71" s="85" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H72" s="64" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H73" s="80" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H74" s="64" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H75" s="80" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H76" s="65" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H77" s="66" t="s">
         <v>190</v>
       </c>
@@ -8218,6 +8213,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -8355,7 +8356,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8364,22 +8365,39 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C263E3-2AA1-43E0-8AC9-C7C66277B332}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615D0308-A962-4273-9D27-8D7E6C533D14}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BE13FA5-2B48-4235-B442-8317F2373CFA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C263E3-2AA1-43E0-8AC9-C7C66277B332}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615D0308-A962-4273-9D27-8D7E6C533D14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BE13FA5-2B48-4235-B442-8317F2373CFA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/SSIS-Project/Timesheets/Buhle/Buhle_Mukhuba_March_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Buhle/Buhle_Mukhuba_March_FinalWeek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_TeolanGovender_2026\SSIS-Project\Timesheets\Buhle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E531877-99BB-4008-B1F2-A257D126D609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22393A1-379E-4FC9-AA75-A6FD792D6241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -723,7 +723,7 @@
     <t>Udemy course - Excel for beginners</t>
   </si>
   <si>
-    <t>Attended onboarding meeting and started working on dream board update</t>
+    <t>Attended onboarding meeting and started working on dream board</t>
   </si>
 </sst>
 </file>
@@ -2146,7 +2146,7 @@
       <c r="I9" s="33"/>
       <c r="J9" s="33"/>
     </row>
-    <row r="10" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="20">
         <v>46083</v>
       </c>
@@ -8219,6 +8219,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -8356,15 +8365,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615D0308-A962-4273-9D27-8D7E6C533D14}">
   <ds:schemaRefs>
@@ -8375,6 +8375,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BE13FA5-2B48-4235-B442-8317F2373CFA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C263E3-2AA1-43E0-8AC9-C7C66277B332}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8392,14 +8400,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BE13FA5-2B48-4235-B442-8317F2373CFA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{5138fff4-6130-46cf-adb5-ec5d984d54d5}" enabled="1" method="Privileged" siteId="{174c7352-9c5c-4558-b848-be140b444e7d}" removed="0"/>

--- a/SSIS-Project/Timesheets/Buhle/Buhle_Mukhuba_March_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Buhle/Buhle_Mukhuba_March_FinalWeek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_TeolanGovender_2026\SSIS-Project\Timesheets\Buhle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22393A1-379E-4FC9-AA75-A6FD792D6241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4313190B-4E40-4581-8FC8-722C27E061DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>

--- a/SSIS-Project/Timesheets/Buhle/Buhle_Mukhuba_March_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Buhle/Buhle_Mukhuba_March_FinalWeek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_TeolanGovender_2026\SSIS-Project\Timesheets\Buhle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4313190B-4E40-4581-8FC8-722C27E061DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4018516-02C6-4E5D-BBF3-4AF1476CA0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -633,9 +633,6 @@
     <t>Buhle</t>
   </si>
   <si>
-    <t>Continued working on dream board</t>
-  </si>
-  <si>
     <t>Attended full day onboarding at the station office</t>
   </si>
   <si>
@@ -724,6 +721,9 @@
   </si>
   <si>
     <t>Attended onboarding meeting and started working on dream board</t>
+  </si>
+  <si>
+    <t>Continued working on dream board - update</t>
   </si>
 </sst>
 </file>
@@ -2164,7 +2164,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H10" s="27">
         <f>J10-I10</f>
@@ -2177,7 +2177,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="20">
         <v>46083</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>15</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="H11" s="27">
         <f>J11-I11</f>
@@ -2226,7 +2226,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H12" s="27">
         <f t="shared" ref="H12:H84" si="0">J12-I12</f>
@@ -2257,7 +2257,7 @@
         <v>15</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H13" s="27">
         <f t="shared" si="0"/>
@@ -2288,7 +2288,7 @@
         <v>15</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H14" s="27">
         <f t="shared" si="0"/>
@@ -2319,7 +2319,7 @@
         <v>15</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H15" s="27">
         <f t="shared" si="0"/>
@@ -2350,7 +2350,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H16" s="27">
         <f t="shared" si="0"/>
@@ -2381,7 +2381,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H17" s="27">
         <f t="shared" si="0"/>
@@ -2412,7 +2412,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H18" s="27">
         <f t="shared" si="0"/>
@@ -2443,7 +2443,7 @@
         <v>15</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H19" s="27">
         <f t="shared" si="0"/>
@@ -2474,7 +2474,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H20" s="27">
         <f t="shared" si="0"/>
@@ -2505,7 +2505,7 @@
         <v>15</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H21" s="27">
         <f t="shared" si="0"/>
@@ -2536,7 +2536,7 @@
         <v>15</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H22" s="27">
         <f t="shared" si="0"/>
@@ -2567,7 +2567,7 @@
         <v>15</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H23" s="27">
         <f t="shared" si="0"/>
@@ -2598,7 +2598,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H24" s="27">
         <f t="shared" si="0"/>
@@ -2629,7 +2629,7 @@
         <v>15</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H25" s="27">
         <f t="shared" si="0"/>
@@ -2660,7 +2660,7 @@
         <v>15</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H26" s="27">
         <f>J26-I26</f>
@@ -2729,7 +2729,7 @@
         <v>15</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H29" s="27">
         <f t="shared" si="0"/>
@@ -2760,7 +2760,7 @@
         <v>15</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H30" s="27">
         <f t="shared" si="0"/>
@@ -2791,7 +2791,7 @@
         <v>15</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H31" s="27">
         <f t="shared" si="0"/>
@@ -2822,7 +2822,7 @@
         <v>15</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H32" s="27">
         <f t="shared" si="0"/>
@@ -2853,7 +2853,7 @@
         <v>15</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H33" s="27">
         <f t="shared" si="0"/>
@@ -2884,7 +2884,7 @@
         <v>15</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H34" s="27">
         <f t="shared" si="0"/>
@@ -2915,7 +2915,7 @@
         <v>15</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H35" s="27">
         <f t="shared" si="0"/>
@@ -2946,7 +2946,7 @@
         <v>15</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H36" s="27">
         <f t="shared" si="0"/>
@@ -2977,7 +2977,7 @@
         <v>15</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H37" s="27">
         <f t="shared" si="0"/>
@@ -3008,7 +3008,7 @@
         <v>15</v>
       </c>
       <c r="G38" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H38" s="27">
         <f t="shared" si="0"/>
@@ -3039,7 +3039,7 @@
         <v>15</v>
       </c>
       <c r="G39" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H39" s="27">
         <f t="shared" si="0"/>
@@ -3070,7 +3070,7 @@
         <v>15</v>
       </c>
       <c r="G40" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H40" s="27">
         <f t="shared" si="0"/>
@@ -3101,7 +3101,7 @@
         <v>15</v>
       </c>
       <c r="G41" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H41" s="27">
         <f t="shared" si="0"/>
@@ -3132,7 +3132,7 @@
         <v>15</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H42" s="27">
         <f t="shared" si="0"/>
@@ -3163,7 +3163,7 @@
         <v>15</v>
       </c>
       <c r="G43" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H43" s="27">
         <f t="shared" si="0"/>
@@ -3194,7 +3194,7 @@
         <v>15</v>
       </c>
       <c r="G44" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H44" s="27">
         <f t="shared" si="0"/>
@@ -3225,7 +3225,7 @@
         <v>15</v>
       </c>
       <c r="G45" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="0"/>
@@ -3256,7 +3256,7 @@
         <v>15</v>
       </c>
       <c r="G46" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H46" s="27">
         <f t="shared" si="0"/>
@@ -3286,7 +3286,7 @@
         <v>15</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H47" s="27">
         <f t="shared" si="0"/>
@@ -3317,7 +3317,7 @@
         <v>15</v>
       </c>
       <c r="G48" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H48" s="27">
         <f t="shared" si="0"/>
@@ -3348,7 +3348,7 @@
         <v>15</v>
       </c>
       <c r="G49" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H49" s="27">
         <f t="shared" si="0"/>
@@ -3379,7 +3379,7 @@
         <v>15</v>
       </c>
       <c r="G50" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H50" s="27">
         <f t="shared" si="0"/>
@@ -3410,7 +3410,7 @@
         <v>15</v>
       </c>
       <c r="G51" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H51" s="27">
         <f t="shared" si="0"/>
@@ -3441,7 +3441,7 @@
         <v>15</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H52" s="27">
         <f t="shared" si="0"/>
@@ -3472,7 +3472,7 @@
         <v>15</v>
       </c>
       <c r="G53" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H53" s="27">
         <f t="shared" si="0"/>
@@ -3503,7 +3503,7 @@
         <v>15</v>
       </c>
       <c r="G54" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H54" s="27">
         <f t="shared" si="0"/>
@@ -3534,7 +3534,7 @@
         <v>15</v>
       </c>
       <c r="G55" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="0"/>
@@ -3565,7 +3565,7 @@
         <v>15</v>
       </c>
       <c r="G56" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H56" s="27">
         <f t="shared" si="0"/>
@@ -3596,7 +3596,7 @@
         <v>15</v>
       </c>
       <c r="G57" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H57" s="27">
         <f t="shared" si="0"/>
@@ -3627,7 +3627,7 @@
         <v>15</v>
       </c>
       <c r="G58" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H58" s="27">
         <f t="shared" si="0"/>
@@ -3658,7 +3658,7 @@
         <v>15</v>
       </c>
       <c r="G59" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H59" s="27">
         <f t="shared" si="0"/>
@@ -3689,7 +3689,7 @@
         <v>15</v>
       </c>
       <c r="G60" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H60" s="27">
         <f t="shared" si="0"/>
@@ -3720,7 +3720,7 @@
         <v>15</v>
       </c>
       <c r="G61" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H61" s="27">
         <f t="shared" si="0"/>
@@ -3751,7 +3751,7 @@
         <v>15</v>
       </c>
       <c r="G62" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H62" s="27">
         <f t="shared" si="0"/>
@@ -3782,7 +3782,7 @@
         <v>15</v>
       </c>
       <c r="G63" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H63" s="27">
         <f t="shared" si="0"/>
@@ -3851,7 +3851,7 @@
         <v>15</v>
       </c>
       <c r="G66" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H66" s="27">
         <f t="shared" si="0"/>
@@ -3882,7 +3882,7 @@
         <v>15</v>
       </c>
       <c r="G67" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H67" s="27">
         <f t="shared" si="0"/>
@@ -3913,7 +3913,7 @@
         <v>15</v>
       </c>
       <c r="G68" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H68" s="27">
         <f t="shared" si="0"/>
@@ -3944,7 +3944,7 @@
         <v>15</v>
       </c>
       <c r="G69" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H69" s="27">
         <f t="shared" si="0"/>
@@ -3975,7 +3975,7 @@
         <v>15</v>
       </c>
       <c r="G70" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H70" s="27">
         <f t="shared" si="0"/>
@@ -4006,7 +4006,7 @@
         <v>15</v>
       </c>
       <c r="G71" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H71" s="27">
         <f t="shared" si="0"/>
@@ -4037,7 +4037,7 @@
         <v>15</v>
       </c>
       <c r="G72" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H72" s="27">
         <f t="shared" si="0"/>
@@ -4068,7 +4068,7 @@
         <v>15</v>
       </c>
       <c r="G73" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H73" s="27">
         <f t="shared" si="0"/>
@@ -4099,7 +4099,7 @@
         <v>15</v>
       </c>
       <c r="G74" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H74" s="27">
         <f t="shared" si="0"/>
@@ -4130,7 +4130,7 @@
         <v>15</v>
       </c>
       <c r="G75" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H75" s="27">
         <f t="shared" si="0"/>
@@ -4161,7 +4161,7 @@
         <v>15</v>
       </c>
       <c r="G76" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H76" s="27">
         <f t="shared" si="0"/>
@@ -4192,7 +4192,7 @@
         <v>15</v>
       </c>
       <c r="G77" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H77" s="27">
         <f t="shared" si="0"/>
@@ -4223,7 +4223,7 @@
         <v>15</v>
       </c>
       <c r="G78" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H78" s="27">
         <f t="shared" si="0"/>
@@ -4254,7 +4254,7 @@
         <v>15</v>
       </c>
       <c r="G79" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H79" s="27">
         <f t="shared" si="0"/>
@@ -4285,7 +4285,7 @@
         <v>15</v>
       </c>
       <c r="G80" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H80" s="27">
         <f t="shared" si="0"/>
@@ -4316,7 +4316,7 @@
         <v>15</v>
       </c>
       <c r="G81" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H81" s="27">
         <f t="shared" si="0"/>
@@ -4347,7 +4347,7 @@
         <v>15</v>
       </c>
       <c r="G82" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H82" s="27">
         <f t="shared" si="0"/>
@@ -4378,7 +4378,7 @@
         <v>15</v>
       </c>
       <c r="G83" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H83" s="27">
         <f t="shared" si="0"/>
@@ -4409,7 +4409,7 @@
         <v>15</v>
       </c>
       <c r="G84" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H84" s="27">
         <f t="shared" si="0"/>
@@ -4440,7 +4440,7 @@
         <v>15</v>
       </c>
       <c r="G85" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H85" s="27">
         <f t="shared" ref="H85:H93" si="1">J85-I85</f>
@@ -4471,7 +4471,7 @@
         <v>15</v>
       </c>
       <c r="G86" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H86" s="27">
         <f t="shared" si="1"/>
@@ -4502,7 +4502,7 @@
         <v>15</v>
       </c>
       <c r="G87" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H87" s="27">
         <f t="shared" si="1"/>
@@ -4523,7 +4523,7 @@
       <c r="E88" s="25"/>
       <c r="F88" s="25"/>
       <c r="G88" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H88" s="27">
         <f t="shared" si="1"/>
@@ -4554,7 +4554,7 @@
         <v>15</v>
       </c>
       <c r="G89" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H89" s="27">
         <f t="shared" si="1"/>
@@ -4585,7 +4585,7 @@
         <v>15</v>
       </c>
       <c r="G90" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H90" s="27">
         <f t="shared" si="1"/>
@@ -4616,7 +4616,7 @@
         <v>15</v>
       </c>
       <c r="G91" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H91" s="27">
         <f t="shared" si="1"/>
@@ -4647,7 +4647,7 @@
         <v>15</v>
       </c>
       <c r="G92" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H92" s="27">
         <f t="shared" si="1"/>
@@ -4678,7 +4678,7 @@
         <v>15</v>
       </c>
       <c r="G93" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H93" s="27">
         <f t="shared" si="1"/>
@@ -4709,7 +4709,7 @@
         <v>15</v>
       </c>
       <c r="G94" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H94" s="27">
         <f t="shared" ref="H94:H102" si="2">J94-I94</f>
@@ -4740,7 +4740,7 @@
         <v>15</v>
       </c>
       <c r="G95" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H95" s="27">
         <f t="shared" si="2"/>
@@ -4771,7 +4771,7 @@
         <v>15</v>
       </c>
       <c r="G96" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H96" s="27">
         <f t="shared" si="2"/>
@@ -4802,7 +4802,7 @@
         <v>15</v>
       </c>
       <c r="G97" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H97" s="27">
         <f t="shared" si="2"/>
@@ -4833,7 +4833,7 @@
         <v>15</v>
       </c>
       <c r="G98" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H98" s="27">
         <f t="shared" si="2"/>
@@ -4864,7 +4864,7 @@
         <v>15</v>
       </c>
       <c r="G99" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H99" s="27">
         <f t="shared" si="2"/>
@@ -4895,7 +4895,7 @@
         <v>15</v>
       </c>
       <c r="G100" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H100" s="27">
         <f t="shared" si="2"/>
@@ -4926,7 +4926,7 @@
         <v>15</v>
       </c>
       <c r="G101" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H101" s="27">
         <f t="shared" si="2"/>
@@ -4957,7 +4957,7 @@
         <v>15</v>
       </c>
       <c r="G102" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H102" s="27">
         <f t="shared" si="2"/>
@@ -4988,7 +4988,7 @@
         <v>15</v>
       </c>
       <c r="G103" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H103" s="27">
         <f>J103-I103</f>
@@ -5019,7 +5019,7 @@
         <v>15</v>
       </c>
       <c r="G104" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H104" s="27">
         <f t="shared" ref="H104:H112" si="3">J104-I104</f>
@@ -5050,7 +5050,7 @@
         <v>15</v>
       </c>
       <c r="G105" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H105" s="27">
         <f t="shared" si="3"/>
@@ -5081,7 +5081,7 @@
         <v>15</v>
       </c>
       <c r="G106" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H106" s="27">
         <f t="shared" si="3"/>
@@ -5112,7 +5112,7 @@
         <v>15</v>
       </c>
       <c r="G107" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H107" s="27">
         <f t="shared" si="3"/>
@@ -5143,7 +5143,7 @@
         <v>15</v>
       </c>
       <c r="G108" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H108" s="27">
         <f t="shared" si="3"/>
@@ -5174,7 +5174,7 @@
         <v>15</v>
       </c>
       <c r="G109" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H109" s="27">
         <f t="shared" si="3"/>
@@ -5205,7 +5205,7 @@
         <v>15</v>
       </c>
       <c r="G110" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H110" s="27">
         <f t="shared" si="3"/>
@@ -5236,7 +5236,7 @@
         <v>15</v>
       </c>
       <c r="G111" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H111" s="27">
         <f t="shared" si="3"/>
@@ -5267,7 +5267,7 @@
         <v>15</v>
       </c>
       <c r="G112" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H112" s="27">
         <f t="shared" si="3"/>
@@ -5298,7 +5298,7 @@
         <v>15</v>
       </c>
       <c r="G113" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H113" s="27">
         <f t="shared" ref="H113:H176" si="4">J113-I113</f>
@@ -5379,7 +5379,7 @@
         <v>15</v>
       </c>
       <c r="G116" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H116" s="27">
         <f t="shared" si="4"/>
@@ -5410,7 +5410,7 @@
         <v>15</v>
       </c>
       <c r="G117" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H117" s="27">
         <f t="shared" si="4"/>
@@ -5441,7 +5441,7 @@
         <v>15</v>
       </c>
       <c r="G118" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H118" s="27">
         <f t="shared" si="4"/>
@@ -5472,7 +5472,7 @@
         <v>15</v>
       </c>
       <c r="G119" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H119" s="27">
         <f t="shared" si="4"/>
@@ -5503,7 +5503,7 @@
         <v>15</v>
       </c>
       <c r="G120" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H120" s="27">
         <f t="shared" si="4"/>
@@ -5534,7 +5534,7 @@
         <v>15</v>
       </c>
       <c r="G121" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H121" s="27">
         <f t="shared" si="4"/>
@@ -5565,7 +5565,7 @@
         <v>15</v>
       </c>
       <c r="G122" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H122" s="27">
         <f t="shared" si="4"/>
@@ -5596,7 +5596,7 @@
         <v>15</v>
       </c>
       <c r="G123" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H123" s="27">
         <f t="shared" si="4"/>
@@ -5627,7 +5627,7 @@
         <v>15</v>
       </c>
       <c r="G124" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H124" s="27">
         <f t="shared" si="4"/>
@@ -5658,7 +5658,7 @@
         <v>15</v>
       </c>
       <c r="G125" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H125" s="27">
         <f t="shared" si="4"/>
@@ -5689,7 +5689,7 @@
         <v>15</v>
       </c>
       <c r="G126" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H126" s="27">
         <f t="shared" si="4"/>
@@ -5720,7 +5720,7 @@
         <v>15</v>
       </c>
       <c r="G127" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H127" s="27">
         <f t="shared" si="4"/>
@@ -5751,7 +5751,7 @@
         <v>15</v>
       </c>
       <c r="G128" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H128" s="27">
         <f t="shared" si="4"/>
@@ -5782,7 +5782,7 @@
         <v>15</v>
       </c>
       <c r="G129" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H129" s="27">
         <f t="shared" si="4"/>
@@ -5813,7 +5813,7 @@
         <v>15</v>
       </c>
       <c r="G130" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H130" s="27">
         <f t="shared" si="4"/>
@@ -5844,7 +5844,7 @@
         <v>15</v>
       </c>
       <c r="G131" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H131" s="27">
         <f t="shared" si="4"/>
@@ -5875,7 +5875,7 @@
         <v>15</v>
       </c>
       <c r="G132" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H132" s="27">
         <f t="shared" si="4"/>
@@ -5906,7 +5906,7 @@
         <v>15</v>
       </c>
       <c r="G133" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H133" s="27">
         <f t="shared" si="4"/>
@@ -5937,7 +5937,7 @@
         <v>15</v>
       </c>
       <c r="G134" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H134" s="27">
         <f t="shared" si="4"/>
@@ -5968,7 +5968,7 @@
         <v>15</v>
       </c>
       <c r="G135" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H135" s="27">
         <f>J135-I135</f>
@@ -5999,7 +5999,7 @@
         <v>15</v>
       </c>
       <c r="G136" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H136" s="27">
         <f t="shared" ref="H136:H144" si="5">J136-I136</f>
@@ -6030,7 +6030,7 @@
         <v>15</v>
       </c>
       <c r="G137" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H137" s="27">
         <f t="shared" si="5"/>
@@ -6061,7 +6061,7 @@
         <v>15</v>
       </c>
       <c r="G138" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H138" s="27">
         <f t="shared" si="5"/>
@@ -6092,7 +6092,7 @@
         <v>15</v>
       </c>
       <c r="G139" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H139" s="27">
         <f t="shared" si="5"/>
@@ -6123,7 +6123,7 @@
         <v>15</v>
       </c>
       <c r="G140" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H140" s="27">
         <f t="shared" si="5"/>
@@ -6154,7 +6154,7 @@
         <v>15</v>
       </c>
       <c r="G141" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H141" s="27">
         <f t="shared" si="5"/>
@@ -6185,7 +6185,7 @@
         <v>15</v>
       </c>
       <c r="G142" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H142" s="27">
         <f t="shared" si="5"/>
@@ -6216,7 +6216,7 @@
         <v>15</v>
       </c>
       <c r="G143" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H143" s="27">
         <f t="shared" si="5"/>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="G144" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H144" s="27">
         <f t="shared" si="5"/>
@@ -6278,7 +6278,7 @@
         <v>15</v>
       </c>
       <c r="G145" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H145" s="27">
         <f t="shared" si="4"/>
@@ -6309,7 +6309,7 @@
         <v>15</v>
       </c>
       <c r="G146" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H146" s="27">
         <f t="shared" si="4"/>
@@ -6340,7 +6340,7 @@
         <v>15</v>
       </c>
       <c r="G147" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H147" s="27">
         <f t="shared" si="4"/>
@@ -6371,7 +6371,7 @@
         <v>15</v>
       </c>
       <c r="G148" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H148" s="27">
         <f t="shared" si="4"/>
@@ -6402,7 +6402,7 @@
         <v>15</v>
       </c>
       <c r="G149" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H149" s="27">
         <f t="shared" si="4"/>
@@ -6433,7 +6433,7 @@
         <v>15</v>
       </c>
       <c r="G150" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H150" s="27">
         <f t="shared" si="4"/>
@@ -6464,7 +6464,7 @@
         <v>15</v>
       </c>
       <c r="G151" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H151" s="27">
         <f t="shared" si="4"/>
@@ -6495,7 +6495,7 @@
         <v>15</v>
       </c>
       <c r="G152" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H152" s="27">
         <f t="shared" si="4"/>
@@ -6526,7 +6526,7 @@
         <v>15</v>
       </c>
       <c r="G153" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H153" s="27">
         <f t="shared" si="4"/>
@@ -6557,7 +6557,7 @@
         <v>15</v>
       </c>
       <c r="G154" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H154" s="27">
         <f t="shared" si="4"/>
@@ -6588,7 +6588,7 @@
         <v>15</v>
       </c>
       <c r="G155" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H155" s="27">
         <f t="shared" si="4"/>
@@ -6619,7 +6619,7 @@
         <v>15</v>
       </c>
       <c r="G156" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H156" s="27">
         <f t="shared" si="4"/>
@@ -6650,7 +6650,7 @@
         <v>15</v>
       </c>
       <c r="G157" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H157" s="27">
         <f t="shared" si="4"/>
@@ -6681,7 +6681,7 @@
         <v>15</v>
       </c>
       <c r="G158" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H158" s="27">
         <f t="shared" si="4"/>
@@ -6712,7 +6712,7 @@
         <v>15</v>
       </c>
       <c r="G159" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H159" s="27">
         <f t="shared" si="4"/>
@@ -6743,7 +6743,7 @@
         <v>15</v>
       </c>
       <c r="G160" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H160" s="27">
         <f t="shared" si="4"/>
@@ -6774,7 +6774,7 @@
         <v>15</v>
       </c>
       <c r="G161" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H161" s="27">
         <f t="shared" si="4"/>
@@ -6805,7 +6805,7 @@
         <v>15</v>
       </c>
       <c r="G162" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H162" s="27">
         <f t="shared" si="4"/>
@@ -6874,7 +6874,7 @@
         <v>15</v>
       </c>
       <c r="G165" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H165" s="27">
         <f t="shared" si="4"/>
@@ -6905,7 +6905,7 @@
         <v>15</v>
       </c>
       <c r="G166" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H166" s="27">
         <f t="shared" si="4"/>
@@ -6936,7 +6936,7 @@
         <v>15</v>
       </c>
       <c r="G167" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H167" s="27">
         <f t="shared" si="4"/>
@@ -6967,7 +6967,7 @@
         <v>15</v>
       </c>
       <c r="G168" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H168" s="27">
         <f t="shared" si="4"/>
@@ -6998,7 +6998,7 @@
         <v>15</v>
       </c>
       <c r="G169" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H169" s="27">
         <f t="shared" si="4"/>
@@ -7029,7 +7029,7 @@
         <v>15</v>
       </c>
       <c r="G170" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H170" s="27">
         <f t="shared" si="4"/>
@@ -7060,7 +7060,7 @@
         <v>15</v>
       </c>
       <c r="G171" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H171" s="27">
         <f t="shared" si="4"/>
@@ -7091,7 +7091,7 @@
         <v>15</v>
       </c>
       <c r="G172" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H172" s="27">
         <f t="shared" si="4"/>
@@ -7122,7 +7122,7 @@
         <v>15</v>
       </c>
       <c r="G173" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H173" s="27">
         <f t="shared" si="4"/>
@@ -7153,7 +7153,7 @@
         <v>15</v>
       </c>
       <c r="G174" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H174" s="27">
         <f t="shared" si="4"/>
@@ -7184,7 +7184,7 @@
         <v>15</v>
       </c>
       <c r="G175" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H175" s="27">
         <f t="shared" si="4"/>
@@ -7215,7 +7215,7 @@
         <v>15</v>
       </c>
       <c r="G176" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H176" s="27">
         <f t="shared" si="4"/>
@@ -7246,7 +7246,7 @@
         <v>15</v>
       </c>
       <c r="G177" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H177" s="27">
         <f t="shared" ref="H177" si="6">J177-I177</f>
@@ -8219,15 +8219,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -8365,6 +8356,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615D0308-A962-4273-9D27-8D7E6C533D14}">
   <ds:schemaRefs>
@@ -8375,14 +8375,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BE13FA5-2B48-4235-B442-8317F2373CFA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C263E3-2AA1-43E0-8AC9-C7C66277B332}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8400,6 +8392,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BE13FA5-2B48-4235-B442-8317F2373CFA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{5138fff4-6130-46cf-adb5-ec5d984d54d5}" enabled="1" method="Privileged" siteId="{174c7352-9c5c-4558-b848-be140b444e7d}" removed="0"/>
